--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Chara.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Chara.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3316" uniqueCount="2242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3332" uniqueCount="2257">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -2869,6 +2869,9 @@
     <t xml:space="preserve">sorin</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.252</t>
+  </si>
+  <si>
     <t xml:space="preserve">소린</t>
   </si>
   <si>
@@ -2878,13 +2881,13 @@
     <t xml:space="preserve">ソリン</t>
   </si>
   <si>
-    <t xml:space="preserve">대마도사</t>
+    <t xml:space="preserve">마도사</t>
   </si>
   <si>
     <t xml:space="preserve">Magus</t>
   </si>
   <si>
-    <t xml:space="preserve">大魔道士</t>
+    <t xml:space="preserve">魔道士</t>
   </si>
   <si>
     <t xml:space="preserve">vesda</t>
@@ -2941,7 +2944,7 @@
     <t xml:space="preserve">ガーラス</t>
   </si>
   <si>
-    <t xml:space="preserve">블랙 로드</t>
+    <t xml:space="preserve">흑경</t>
   </si>
   <si>
     <t xml:space="preserve">Black Lord</t>
@@ -6587,6 +6590,48 @@
   </si>
   <si>
     <t xml:space="preserve">イノス＝トゥルス2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에이스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eyth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">God of Infidel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">호로메</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ホロメ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월영의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddess of Moonshadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月影の</t>
   </si>
   <si>
     <t xml:space="preserve">ehekatl</t>
@@ -6977,7 +7022,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L531"/>
+  <dimension ref="A1:L533"/>
   <sheetFormatPr defaultColWidth="8.62109375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="0" width="16.15"/>
@@ -11835,202 +11880,202 @@
         <v>947</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>87</v>
+        <v>948</v>
       </c>
       <c r="D240" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="J240" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="K240" s="0" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="L240" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B241" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="J241" s="0" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="K241" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="L241" s="0" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B242" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="J242" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="K242" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="L242" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B243" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D243" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J243" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K243" s="0" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="L243" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B244" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D244" s="0" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E244" s="0" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J244" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="K244" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="L244" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B245" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D245" s="0" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B246" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D246" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B247" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D247" s="0" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B248" s="0" t="s">
         <v>41</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B249" s="0" t="s">
         <v>60</v>
@@ -12045,599 +12090,599 @@
         <v>14</v>
       </c>
       <c r="J249" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K249" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L249" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="0" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B250" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D250" s="0" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="0" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B251" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D251" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B252" s="0" t="s">
         <v>97</v>
       </c>
       <c r="D252" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B253" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D253" s="0" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E253" s="0" t="s">
         <v>1015</v>
       </c>
-      <c r="E253" s="0" t="s">
-        <v>1014</v>
-      </c>
       <c r="F253" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B254" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D254" s="0" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E254" s="0" t="s">
         <v>1018</v>
       </c>
-      <c r="E254" s="0" t="s">
-        <v>1017</v>
-      </c>
       <c r="F254" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D255" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B256" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D256" s="0" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E256" s="0" t="s">
         <v>1026</v>
       </c>
-      <c r="E256" s="0" t="s">
-        <v>1025</v>
-      </c>
       <c r="F256" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B257" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D257" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B258" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B259" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B260" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D260" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E260" s="0" t="s">
         <v>1041</v>
       </c>
-      <c r="E260" s="0" t="s">
-        <v>1040</v>
-      </c>
       <c r="F260" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B261" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J261" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="K261" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="L261" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B262" s="0" t="s">
         <v>97</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J262" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="K262" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L262" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B263" s="0" t="s">
         <v>97</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="J263" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="K263" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="L263" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B264" s="0" t="s">
         <v>449</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="J264" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="K264" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="L264" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B265" s="0" t="s">
         <v>449</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="J265" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="K265" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="L265" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B266" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D266" s="0" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E266" s="0" t="s">
         <v>1075</v>
       </c>
-      <c r="E266" s="0" t="s">
-        <v>1074</v>
-      </c>
       <c r="F266" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B267" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D267" s="0" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E267" s="0" t="s">
         <v>1078</v>
       </c>
-      <c r="E267" s="0" t="s">
-        <v>1077</v>
-      </c>
       <c r="F267" s="0" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="0" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B268" s="0" t="s">
         <v>158</v>
       </c>
       <c r="D268" s="0" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E268" s="0" t="s">
         <v>1081</v>
       </c>
-      <c r="E268" s="0" t="s">
-        <v>1080</v>
-      </c>
       <c r="F268" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B269" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B270" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D270" s="0" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E270" s="0" t="s">
         <v>1088</v>
       </c>
-      <c r="E270" s="0" t="s">
-        <v>1087</v>
-      </c>
       <c r="F270" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B271" s="0" t="s">
         <v>97</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B272" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B273" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D273" s="0" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E273" s="0" t="s">
         <v>1099</v>
       </c>
-      <c r="E273" s="0" t="s">
-        <v>1098</v>
-      </c>
       <c r="F273" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="0" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B274" s="0" t="s">
         <v>499</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="0" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B275" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B276" s="0" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="0" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B277" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D277" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E277" s="0" t="s">
         <v>1115</v>
       </c>
-      <c r="E277" s="0" t="s">
-        <v>1114</v>
-      </c>
       <c r="F277" s="0" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="0" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B278" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B279" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D279" s="0" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="0" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B280" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="J280" s="0" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="K280" s="0" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="L280" s="0" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="0" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B281" s="0" t="s">
         <v>898</v>
@@ -12652,21 +12697,21 @@
         <v>14</v>
       </c>
       <c r="J281" s="0" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="K281" s="0" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="L281" s="0" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="0" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B282" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>14</v>
@@ -12689,7 +12734,7 @@
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="0" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B283" s="0" t="s">
         <v>60</v>
@@ -12704,689 +12749,689 @@
         <v>14</v>
       </c>
       <c r="J283" s="0" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="K283" s="0" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="L283" s="0" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="0" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B284" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D284" s="0" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="0" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B285" s="0" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="0" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B286" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="J286" s="0" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="K286" s="0" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="L286" s="0" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="0" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B287" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="J287" s="0" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="K287" s="0" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="L287" s="0" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="0" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B288" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D288" s="0" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E288" s="0" t="s">
         <v>1165</v>
       </c>
-      <c r="E288" s="0" t="s">
-        <v>1164</v>
-      </c>
       <c r="F288" s="0" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="0" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B289" s="0" t="s">
         <v>499</v>
       </c>
       <c r="D289" s="0" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="0" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B290" s="0" t="s">
         <v>499</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="0" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B291" s="0" t="s">
         <v>499</v>
       </c>
       <c r="D291" s="0" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="0" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B292" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D292" s="0" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J292" s="0" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="K292" s="0" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="L292" s="0" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="0" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B293" s="0" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J293" s="0" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="K293" s="0" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="L293" s="0" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="0" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B294" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D294" s="0" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="0" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B295" s="0" t="s">
         <v>898</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="0" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B296" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D296" s="0" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="J296" s="0" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="K296" s="0" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="L296" s="0" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="0" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B297" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D297" s="0" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E297" s="0" t="s">
         <v>1210</v>
       </c>
-      <c r="E297" s="0" t="s">
-        <v>1209</v>
-      </c>
       <c r="F297" s="0" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="0" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B298" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D298" s="0" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E298" s="0" t="s">
         <v>1213</v>
       </c>
-      <c r="E298" s="0" t="s">
-        <v>1212</v>
-      </c>
       <c r="F298" s="0" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="0" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B299" s="0" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="0" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B300" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="0" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B301" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D301" s="0" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E301" s="0" t="s">
         <v>1225</v>
       </c>
-      <c r="E301" s="0" t="s">
-        <v>1224</v>
-      </c>
       <c r="F301" s="0" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="0" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B302" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="0" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B303" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="J303" s="0" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="K303" s="0" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="L303" s="0" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="0" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B304" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D304" s="0" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E304" s="0" t="s">
         <v>1239</v>
       </c>
-      <c r="E304" s="0" t="s">
-        <v>1238</v>
-      </c>
       <c r="F304" s="0" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="0" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B305" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="0" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B306" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="E306" s="0" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="J306" s="0" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="K306" s="0" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="L306" s="0" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="0" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B307" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="J307" s="0" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="K307" s="0" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="L307" s="0" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="0" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B308" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="0" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B309" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="0" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B310" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="0" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B311" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="0" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B312" s="0" t="s">
         <v>29</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="0" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B313" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J313" s="0" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="K313" s="0" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="L313" s="0" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="0" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B314" s="0" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D314" s="0" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E314" s="0" t="s">
         <v>1284</v>
       </c>
-      <c r="E314" s="0" t="s">
-        <v>1283</v>
-      </c>
       <c r="F314" s="0" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="0" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B315" s="0" t="s">
         <v>534</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="E315" s="0" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="0" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B316" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D316" s="0" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="E316" s="0" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="J316" s="0" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="K316" s="0" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="L316" s="0" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="0" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B317" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="0" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B318" s="0" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="D318" s="0" t="s">
         <v>14</v>
@@ -13398,18 +13443,18 @@
         <v>14</v>
       </c>
       <c r="J318" s="0" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="K318" s="0" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="L318" s="0" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="0" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B319" s="0" t="s">
         <v>13</v>
@@ -13424,404 +13469,404 @@
         <v>14</v>
       </c>
       <c r="J319" s="0" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="K319" s="0" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="L319" s="0" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="0" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B320" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D320" s="0" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E320" s="0" t="s">
         <v>1311</v>
       </c>
-      <c r="E320" s="0" t="s">
-        <v>1310</v>
-      </c>
       <c r="F320" s="0" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="0" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B321" s="0" t="s">
         <v>422</v>
       </c>
       <c r="D321" s="0" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="0" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B322" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D322" s="0" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E322" s="0" t="s">
         <v>1318</v>
       </c>
-      <c r="E322" s="0" t="s">
-        <v>1317</v>
-      </c>
       <c r="F322" s="0" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="0" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B323" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E323" s="0" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="0" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B324" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="0" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B325" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D325" s="0" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E325" s="0" t="s">
         <v>1329</v>
       </c>
-      <c r="E325" s="0" t="s">
-        <v>1328</v>
-      </c>
       <c r="F325" s="0" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="0" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B326" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="E326" s="0" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="F326" s="0" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="0" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B327" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="E327" s="0" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F327" s="0" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="0" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B328" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D328" s="0" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E328" s="0" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="F328" s="0" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="0" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B329" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F329" s="0" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="J329" s="0" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="K329" s="0" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="L329" s="0" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="0" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B330" s="0" t="s">
         <v>449</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E330" s="0" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J330" s="0" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="K330" s="0" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="L330" s="0" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="0" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B331" s="0" t="s">
         <v>219</v>
       </c>
       <c r="D331" s="0" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E331" s="0" t="s">
         <v>1358</v>
       </c>
-      <c r="E331" s="0" t="s">
-        <v>1357</v>
-      </c>
       <c r="F331" s="0" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="J331" s="0" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="K331" s="0" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="L331" s="0" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="0" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B332" s="0" t="s">
         <v>449</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E332" s="0" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="F332" s="0" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="J332" s="0" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="K332" s="0" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="L332" s="0" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="0" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B333" s="0" t="s">
         <v>333</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E333" s="0" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="F333" s="0" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="J333" s="0" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="K333" s="0" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="L333" s="0" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="0" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B334" s="0" t="s">
         <v>219</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E334" s="0" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="F334" s="0" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="J334" s="0" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="K334" s="0" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="L334" s="0" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="0" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B335" s="0" t="s">
         <v>219</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="F335" s="0" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="0" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B336" s="0" t="s">
         <v>534</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="E336" s="0" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="0" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B337" s="0" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="E337" s="0" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="J337" s="0" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="K337" s="0" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="L337" s="0" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="0" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B338" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="E338" s="0" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="0" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B339" s="0" t="s">
         <v>13</v>
@@ -13836,35 +13881,35 @@
         <v>14</v>
       </c>
       <c r="J339" s="0" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="K339" s="0" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="L339" s="0" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="0" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B340" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D340" s="0" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E340" s="0" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="F340" s="0" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="0" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B341" s="0" t="s">
         <v>13</v>
@@ -13879,18 +13924,18 @@
         <v>14</v>
       </c>
       <c r="J341" s="0" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="K341" s="0" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="L341" s="0" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="0" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B342" s="0" t="s">
         <v>13</v>
@@ -13905,206 +13950,206 @@
         <v>14</v>
       </c>
       <c r="J342" s="0" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="K342" s="0" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="L342" s="0" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="0" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B343" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D343" s="0" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="F343" s="0" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="0" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B344" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="F344" s="0" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="0" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B345" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F345" s="0" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="0" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B346" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D346" s="0" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="E346" s="0" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="F346" s="0" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="0" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B347" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="E347" s="0" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="F347" s="0" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="0" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B348" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="E348" s="0" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="F348" s="0" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="0" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B349" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="E349" s="0" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="F349" s="0" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="J349" s="0" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="K349" s="0" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="L349" s="0" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="0" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B350" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="0" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B351" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D351" s="0" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E351" s="0" t="s">
         <v>1452</v>
       </c>
-      <c r="E351" s="0" t="s">
-        <v>1451</v>
-      </c>
       <c r="F351" s="0" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="0" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B352" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D352" s="0" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="J352" s="0" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="K352" s="0" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="L352" s="0" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="0" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B353" s="0" t="s">
         <v>13</v>
@@ -14119,35 +14164,35 @@
         <v>14</v>
       </c>
       <c r="J353" s="0" t="s">
+        <v>1460</v>
+      </c>
+      <c r="K353" s="0" t="s">
         <v>1459</v>
       </c>
-      <c r="K353" s="0" t="s">
-        <v>1458</v>
-      </c>
       <c r="L353" s="0" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="0" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B354" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="E354" s="0" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="F354" s="0" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="0" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B355" s="0" t="s">
         <v>13</v>
@@ -14162,44 +14207,44 @@
         <v>14</v>
       </c>
       <c r="J355" s="0" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="K355" s="0" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="L355" s="0" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="0" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B356" s="0" t="s">
         <v>735</v>
       </c>
       <c r="D356" s="0" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="J356" s="0" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="K356" s="0" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="L356" s="0" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="0" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B357" s="0" t="s">
         <v>45</v>
@@ -14214,18 +14259,18 @@
         <v>14</v>
       </c>
       <c r="J357" s="0" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="K357" s="0" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="L357" s="0" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="0" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B358" s="0" t="s">
         <v>13</v>
@@ -14240,240 +14285,240 @@
         <v>14</v>
       </c>
       <c r="J358" s="0" t="s">
+        <v>1482</v>
+      </c>
+      <c r="K358" s="0" t="s">
         <v>1481</v>
       </c>
-      <c r="K358" s="0" t="s">
-        <v>1480</v>
-      </c>
       <c r="L358" s="0" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="0" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B359" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D359" s="0" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E359" s="0" t="s">
         <v>1484</v>
       </c>
-      <c r="E359" s="0" t="s">
-        <v>1483</v>
-      </c>
       <c r="F359" s="0" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="0" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B360" s="0" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="0" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B361" s="0" t="s">
         <v>60</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="E361" s="0" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="F361" s="0" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="J361" s="0" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="K361" s="0" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="L361" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="0" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B362" s="0" t="s">
         <v>189</v>
       </c>
       <c r="D362" s="0" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="E362" s="0" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="F362" s="0" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="J362" s="0" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K362" s="0" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="L362" s="0" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="0" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B363" s="0" t="s">
         <v>189</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="0" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B364" s="0" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D364" s="0" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="0" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B365" s="0" t="s">
         <v>189</v>
       </c>
       <c r="D365" s="0" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F365" s="0" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="0" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B366" s="0" t="s">
         <v>16</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="0" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B367" s="0" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="D367" s="0" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F367" s="0" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="0" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B368" s="0" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="D368" s="0" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="F368" s="0" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="0" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B369" s="0" t="s">
         <v>92</v>
       </c>
       <c r="D369" s="0" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="E369" s="0" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="F369" s="0" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="0" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B370" s="0" t="s">
         <v>335</v>
       </c>
       <c r="D370" s="0" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F370" s="0" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="0" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B371" s="0" t="s">
         <v>13</v>
@@ -14488,18 +14533,18 @@
         <v>14</v>
       </c>
       <c r="J371" s="0" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="K371" s="0" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="L371" s="0" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="0" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B372" s="0" t="s">
         <v>13</v>
@@ -14514,18 +14559,18 @@
         <v>14</v>
       </c>
       <c r="J372" s="0" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K372" s="0" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="L372" s="0" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="0" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B373" s="0" t="s">
         <v>13</v>
@@ -14540,47 +14585,47 @@
         <v>14</v>
       </c>
       <c r="J373" s="0" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="K373" s="0" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="L373" s="0" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="0" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B374" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D374" s="0" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="J374" s="0" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="K374" s="0" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="L374" s="0" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="0" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B375" s="0" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>14</v>
@@ -14592,18 +14637,18 @@
         <v>14</v>
       </c>
       <c r="J375" s="0" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="K375" s="0" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="L375" s="0" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="0" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B376" s="0" t="s">
         <v>333</v>
@@ -14618,18 +14663,18 @@
         <v>14</v>
       </c>
       <c r="J376" s="0" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="K376" s="0" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="L376" s="0" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="0" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B377" s="0" t="s">
         <v>60</v>
@@ -14644,18 +14689,18 @@
         <v>14</v>
       </c>
       <c r="J377" s="0" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="K377" s="0" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L377" s="0" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="0" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B378" s="0" t="s">
         <v>29</v>
@@ -14670,231 +14715,231 @@
         <v>14</v>
       </c>
       <c r="J378" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="K378" s="0" t="s">
         <v>1567</v>
       </c>
-      <c r="K378" s="0" t="s">
-        <v>1566</v>
-      </c>
       <c r="L378" s="0" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="0" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B379" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D379" s="0" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E379" s="0" t="s">
         <v>1570</v>
       </c>
-      <c r="E379" s="0" t="s">
-        <v>1569</v>
-      </c>
       <c r="F379" s="0" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="0" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B380" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D380" s="0" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E380" s="0" t="s">
         <v>1573</v>
       </c>
-      <c r="E380" s="0" t="s">
-        <v>1572</v>
-      </c>
       <c r="F380" s="0" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="0" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B381" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D381" s="0" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E381" s="0" t="s">
         <v>1576</v>
       </c>
-      <c r="E381" s="0" t="s">
-        <v>1575</v>
-      </c>
       <c r="F381" s="0" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="0" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B382" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D382" s="0" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E382" s="0" t="s">
         <v>1579</v>
       </c>
-      <c r="E382" s="0" t="s">
-        <v>1578</v>
-      </c>
       <c r="F382" s="0" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="0" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B383" s="0" t="s">
         <v>60</v>
       </c>
       <c r="D383" s="0" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F383" s="0" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="0" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B384" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D384" s="0" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="E384" s="0" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="F384" s="0" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="0" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B385" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D385" s="0" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="0" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B386" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D386" s="0" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="F386" s="0" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="0" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B387" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D387" s="0" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="E387" s="0" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="F387" s="0" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="0" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B388" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D388" s="0" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="F388" s="0" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="0" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B389" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D389" s="0" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="F389" s="0" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="0" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B390" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D390" s="0" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="E390" s="0" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="F390" s="0" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="J390" s="0" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="K390" s="0" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="L390" s="0" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="0" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B391" s="0" t="s">
         <v>13</v>
@@ -14909,18 +14954,18 @@
         <v>14</v>
       </c>
       <c r="J391" s="0" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="K391" s="0" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="L391" s="0" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="0" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B392" s="0" t="s">
         <v>13</v>
@@ -14935,18 +14980,18 @@
         <v>14</v>
       </c>
       <c r="J392" s="0" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="K392" s="0" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="L392" s="0" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="0" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B393" s="0" t="s">
         <v>333</v>
@@ -14961,18 +15006,18 @@
         <v>14</v>
       </c>
       <c r="J393" s="0" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="K393" s="0" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="L393" s="0" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="0" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B394" s="0" t="s">
         <v>333</v>
@@ -14987,208 +15032,208 @@
         <v>14</v>
       </c>
       <c r="J394" s="0" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="K394" s="0" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L394" s="0" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="0" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B395" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D395" s="0" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="F395" s="0" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="0" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B396" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D396" s="0" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="F396" s="0" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="0" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B397" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="F397" s="0" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="0" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B398" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D398" s="0" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="F398" s="0" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="0" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B399" s="0" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D399" s="0" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E399" s="0" t="s">
         <v>1649</v>
       </c>
-      <c r="D399" s="0" t="s">
-        <v>1650</v>
-      </c>
-      <c r="E399" s="0" t="s">
-        <v>1648</v>
-      </c>
       <c r="F399" s="0" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="0" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B400" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D400" s="0" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="F400" s="0" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="0" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B401" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D401" s="0" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E401" s="0" t="s">
         <v>1657</v>
       </c>
-      <c r="E401" s="0" t="s">
-        <v>1656</v>
-      </c>
       <c r="F401" s="0" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="0" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B402" s="0" t="s">
         <v>534</v>
       </c>
       <c r="D402" s="0" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="E402" s="0" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="F402" s="0" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="0" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B403" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D403" s="0" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="E403" s="0" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="F403" s="0" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="0" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B404" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D404" s="0" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E404" s="0" t="s">
         <v>1668</v>
       </c>
-      <c r="E404" s="0" t="s">
-        <v>1667</v>
-      </c>
       <c r="F404" s="0" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="0" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B405" s="0" t="s">
         <v>333</v>
       </c>
       <c r="D405" s="0" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="E405" s="0" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="F405" s="0" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="0" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B406" s="0" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>14</v>
@@ -15200,18 +15245,18 @@
         <v>14</v>
       </c>
       <c r="J406" s="0" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="K406" s="0" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="L406" s="0" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="0" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B407" s="0" t="s">
         <v>490</v>
@@ -15226,21 +15271,21 @@
         <v>14</v>
       </c>
       <c r="J407" s="0" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="K407" s="0" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="L407" s="0" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="0" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B408" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>14</v>
@@ -15252,44 +15297,44 @@
         <v>14</v>
       </c>
       <c r="J408" s="0" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="K408" s="0" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="L408" s="0" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="0" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B409" s="0" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D409" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E409" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F409" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J409" s="0" t="s">
+        <v>1685</v>
+      </c>
+      <c r="K409" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="L409" s="0" t="s">
         <v>1686</v>
-      </c>
-      <c r="B409" s="0" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D409" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E409" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="F409" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J409" s="0" t="s">
-        <v>1684</v>
-      </c>
-      <c r="K409" s="0" t="s">
-        <v>1620</v>
-      </c>
-      <c r="L409" s="0" t="s">
-        <v>1685</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="0" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B410" s="0" t="s">
         <v>13</v>
@@ -15304,21 +15349,21 @@
         <v>14</v>
       </c>
       <c r="J410" s="0" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="K410" s="0" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="L410" s="0" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="0" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B411" s="0" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>14</v>
@@ -15330,21 +15375,21 @@
         <v>14</v>
       </c>
       <c r="J411" s="0" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="K411" s="0" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="L411" s="0" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="0" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B412" s="0" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>14</v>
@@ -15356,21 +15401,21 @@
         <v>14</v>
       </c>
       <c r="J412" s="0" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="K412" s="0" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="L412" s="0" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="0" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B413" s="0" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>14</v>
@@ -15382,21 +15427,21 @@
         <v>14</v>
       </c>
       <c r="J413" s="0" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="K413" s="0" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="L413" s="0" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="0" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B414" s="0" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>14</v>
@@ -15408,18 +15453,18 @@
         <v>14</v>
       </c>
       <c r="J414" s="0" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="K414" s="0" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="L414" s="0" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="0" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B415" s="0" t="s">
         <v>13</v>
@@ -15434,35 +15479,35 @@
         <v>14</v>
       </c>
       <c r="J415" s="0" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="K415" s="0" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="L415" s="0" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="0" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B416" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D416" s="0" t="s">
+        <v>1711</v>
+      </c>
+      <c r="E416" s="0" t="s">
         <v>1710</v>
       </c>
-      <c r="E416" s="0" t="s">
-        <v>1709</v>
-      </c>
       <c r="F416" s="0" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="0" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B417" s="0" t="s">
         <v>13</v>
@@ -15477,18 +15522,18 @@
         <v>14</v>
       </c>
       <c r="J417" s="0" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="K417" s="0" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="L417" s="0" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="0" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B418" s="0" t="s">
         <v>13</v>
@@ -15503,52 +15548,52 @@
         <v>14</v>
       </c>
       <c r="J418" s="0" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="K418" s="0" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="0" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B419" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D419" s="0" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="E419" s="0" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="F419" s="0" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="0" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B420" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D420" s="0" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E420" s="0" t="s">
         <v>1725</v>
       </c>
-      <c r="E420" s="0" t="s">
-        <v>1724</v>
-      </c>
       <c r="F420" s="0" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="0" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B421" s="0" t="s">
         <v>13</v>
@@ -15563,18 +15608,18 @@
         <v>14</v>
       </c>
       <c r="J421" s="0" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="K421" s="0" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="L421" s="0" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="0" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B422" s="0" t="s">
         <v>665</v>
@@ -15589,18 +15634,18 @@
         <v>14</v>
       </c>
       <c r="J422" s="0" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="K422" s="0" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="L422" s="0" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="0" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B423" s="0" t="s">
         <v>13</v>
@@ -15615,18 +15660,18 @@
         <v>14</v>
       </c>
       <c r="J423" s="0" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="K423" s="0" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="L423" s="0" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="0" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B424" s="0" t="s">
         <v>13</v>
@@ -15641,18 +15686,18 @@
         <v>14</v>
       </c>
       <c r="J424" s="0" t="s">
+        <v>1741</v>
+      </c>
+      <c r="K424" s="0" t="s">
         <v>1740</v>
       </c>
-      <c r="K424" s="0" t="s">
-        <v>1739</v>
-      </c>
       <c r="L424" s="0" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="0" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B425" s="0" t="s">
         <v>45</v>
@@ -15667,69 +15712,69 @@
         <v>14</v>
       </c>
       <c r="J425" s="0" t="s">
+        <v>1744</v>
+      </c>
+      <c r="K425" s="0" t="s">
         <v>1743</v>
       </c>
-      <c r="K425" s="0" t="s">
-        <v>1742</v>
-      </c>
       <c r="L425" s="0" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="0" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B426" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D426" s="0" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="F426" s="0" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="0" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B427" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D427" s="0" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E427" s="0" t="s">
         <v>1750</v>
       </c>
-      <c r="E427" s="0" t="s">
-        <v>1749</v>
-      </c>
       <c r="F427" s="0" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="0" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B428" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D428" s="0" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="F428" s="0" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="0" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B429" s="0" t="s">
         <v>13</v>
@@ -15744,18 +15789,18 @@
         <v>14</v>
       </c>
       <c r="J429" s="0" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K429" s="0" t="s">
         <v>1757</v>
       </c>
-      <c r="K429" s="0" t="s">
-        <v>1756</v>
-      </c>
       <c r="L429" s="0" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="0" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B430" s="0" t="s">
         <v>13</v>
@@ -15770,21 +15815,21 @@
         <v>14</v>
       </c>
       <c r="J430" s="0" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="K430" s="0" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="L430" s="0" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="0" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B431" s="0" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>14</v>
@@ -15796,21 +15841,21 @@
         <v>14</v>
       </c>
       <c r="J431" s="0" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="K431" s="0" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="L431" s="0" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="0" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B432" s="0" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>14</v>
@@ -15822,359 +15867,359 @@
         <v>14</v>
       </c>
       <c r="J432" s="0" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="K432" s="0" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="L432" s="0" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="0" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B433" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D433" s="0" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="E433" s="0" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="F433" s="0" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="J433" s="0" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="K433" s="0" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="L433" s="0" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="0" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B434" s="0" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="D434" s="0" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="E434" s="0" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="F434" s="0" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="0" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B435" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D435" s="0" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="E435" s="0" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="F435" s="0" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="0" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B436" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D436" s="0" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="F436" s="0" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="0" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B437" s="0" t="s">
         <v>60</v>
       </c>
       <c r="D437" s="0" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="E437" s="0" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="F437" s="0" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="0" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B438" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D438" s="0" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="E438" s="0" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="F438" s="0" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="0" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B439" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D439" s="0" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="E439" s="0" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="F439" s="0" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="0" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B440" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D440" s="0" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="F440" s="0" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="0" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B441" s="0" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D441" s="0" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="E441" s="0" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="F441" s="0" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="0" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B442" s="0" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D442" s="0" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E442" s="0" t="s">
         <v>1809</v>
       </c>
-      <c r="E442" s="0" t="s">
-        <v>1808</v>
-      </c>
       <c r="F442" s="0" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="0" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B443" s="0" t="s">
         <v>87</v>
       </c>
       <c r="D443" s="0" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="E443" s="0" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="F443" s="0" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="0" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B444" s="0" t="s">
         <v>176</v>
       </c>
       <c r="D444" s="0" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="E444" s="0" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="F444" s="0" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="0" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B445" s="0" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D445" s="0" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="E445" s="0" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="F445" s="0" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="0" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B446" s="0" t="s">
         <v>176</v>
       </c>
       <c r="D446" s="0" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="E446" s="0" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="F446" s="0" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="0" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B447" s="0" t="s">
         <v>171</v>
       </c>
       <c r="D447" s="0" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="E447" s="0" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="F447" s="0" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="0" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B448" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D448" s="0" t="s">
+        <v>1829</v>
+      </c>
+      <c r="E448" s="0" t="s">
         <v>1828</v>
       </c>
-      <c r="E448" s="0" t="s">
-        <v>1827</v>
-      </c>
       <c r="F448" s="0" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="0" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B449" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D449" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="E449" s="0" t="s">
         <v>1831</v>
       </c>
-      <c r="E449" s="0" t="s">
-        <v>1830</v>
-      </c>
       <c r="F449" s="0" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="0" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B450" s="0" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="D450" s="0" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="F450" s="0" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="0" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B451" s="0" t="s">
         <v>531</v>
       </c>
       <c r="D451" s="0" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="E451" s="0" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="F451" s="0" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="J451" s="0" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="K451" s="0" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="L451" s="0" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="0" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B452" s="0" t="s">
         <v>13</v>
@@ -16189,18 +16234,18 @@
         <v>14</v>
       </c>
       <c r="J452" s="0" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="K452" s="0" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="L452" s="0" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="0" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B453" s="0" t="s">
         <v>16</v>
@@ -16215,18 +16260,18 @@
         <v>14</v>
       </c>
       <c r="J453" s="0" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="K453" s="0" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="L453" s="0" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="0" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B454" s="0" t="s">
         <v>13</v>
@@ -16241,18 +16286,18 @@
         <v>14</v>
       </c>
       <c r="J454" s="0" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="K454" s="0" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="L454" s="0" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="0" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B455" s="0" t="s">
         <v>916</v>
@@ -16267,259 +16312,259 @@
         <v>14</v>
       </c>
       <c r="J455" s="0" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="K455" s="0" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="L455" s="0" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="0" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B456" s="0" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="D456" s="0" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="E456" s="0" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="F456" s="0" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="J456" s="0" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="K456" s="0" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="L456" s="0" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="0" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B457" s="0" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D457" s="0" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="E457" s="0" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="F457" s="0" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="J457" s="0" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="K457" s="0" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="L457" s="0" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="0" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B458" s="0" t="s">
         <v>916</v>
       </c>
       <c r="D458" s="0" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="F458" s="0" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="J458" s="0" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="K458" s="0" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="L458" s="0" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="0" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B459" s="0" t="s">
         <v>916</v>
       </c>
       <c r="D459" s="0" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="E459" s="0" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="F459" s="0" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="J459" s="0" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="K459" s="0" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="L459" s="0" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="0" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B460" s="0" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="D460" s="0" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="F460" s="0" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="0" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B461" s="0" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D461" s="0" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="F461" s="0" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="0" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B462" s="0" t="s">
         <v>499</v>
       </c>
       <c r="D462" s="0" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="E462" s="0" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="F462" s="0" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="0" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B463" s="0" t="s">
         <v>158</v>
       </c>
       <c r="D463" s="0" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="E463" s="0" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="F463" s="0" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="0" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B464" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D464" s="0" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="F464" s="0" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="J464" s="0" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="K464" s="0" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="L464" s="0" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="0" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B465" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D465" s="0" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="E465" s="0" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="F465" s="0" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="0" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B466" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D466" s="0" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E466" s="0" t="s">
         <v>1911</v>
       </c>
-      <c r="E466" s="0" t="s">
+      <c r="F466" s="0" t="s">
+        <v>1913</v>
+      </c>
+      <c r="J466" s="0" t="s">
+        <v>1908</v>
+      </c>
+      <c r="K466" s="0" t="s">
+        <v>1909</v>
+      </c>
+      <c r="L466" s="0" t="s">
         <v>1910</v>
-      </c>
-      <c r="F466" s="0" t="s">
-        <v>1912</v>
-      </c>
-      <c r="J466" s="0" t="s">
-        <v>1907</v>
-      </c>
-      <c r="K466" s="0" t="s">
-        <v>1908</v>
-      </c>
-      <c r="L466" s="0" t="s">
-        <v>1909</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="0" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B467" s="0" t="s">
         <v>13</v>
@@ -16534,70 +16579,70 @@
         <v>14</v>
       </c>
       <c r="J467" s="0" t="s">
+        <v>1915</v>
+      </c>
+      <c r="K467" s="0" t="s">
         <v>1914</v>
       </c>
-      <c r="K467" s="0" t="s">
-        <v>1913</v>
-      </c>
       <c r="L467" s="0" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="0" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B468" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D468" s="0" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="E468" s="0" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="F468" s="0" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="J468" s="0" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="K468" s="0" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="L468" s="0" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="0" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B469" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D469" s="0" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="F469" s="0" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="J469" s="0" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="K469" s="0" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="L469" s="0" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="0" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B470" s="0" t="s">
         <v>13</v>
@@ -16612,315 +16657,315 @@
         <v>14</v>
       </c>
       <c r="J470" s="0" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="K470" s="0" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="L470" s="0" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="0" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="E471" s="0" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="F471" s="0" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="0" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B472" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D472" s="0" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="E472" s="0" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="F472" s="0" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="J472" s="0" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="K472" s="0" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="L472" s="0" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="0" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B473" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D473" s="0" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="E473" s="0" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="F473" s="0" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="0" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B474" s="0" t="s">
         <v>531</v>
       </c>
       <c r="D474" s="0" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="F474" s="0" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="J474" s="0" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="K474" s="0" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="L474" s="0" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="0" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B475" s="0" t="s">
         <v>385</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="E475" s="0" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="F475" s="0" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="J475" s="0" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="K475" s="0" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="L475" s="0" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="0" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B476" s="0" t="s">
         <v>449</v>
       </c>
       <c r="D476" s="0" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="E476" s="0" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="F476" s="0" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="J476" s="0" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="K476" s="0" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="L476" s="0" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="0" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B477" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D477" s="0" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="E477" s="0" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="F477" s="0" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="J477" s="0" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="K477" s="0" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="L477" s="0" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="0" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B478" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D478" s="0" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="F478" s="0" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="J478" s="0" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="K478" s="0" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="L478" s="0" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="0" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B479" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D479" s="0" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="E479" s="0" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="F479" s="0" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="J479" s="0" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="K479" s="0" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="L479" s="0" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="0" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B480" s="0" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D480" s="0" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="E480" s="0" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="F480" s="0" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="J480" s="0" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="K480" s="0" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="L480" s="0" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="0" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B481" s="0" t="s">
         <v>499</v>
       </c>
       <c r="D481" s="0" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="F481" s="0" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="0" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B482" s="0" t="s">
         <v>499</v>
       </c>
       <c r="D482" s="0" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F482" s="0" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="J482" s="0" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="K482" s="0" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="L482" s="0" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="0" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B483" s="0" t="s">
         <v>939</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="F483" s="0" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="J483" s="0" t="s">
         <v>14</v>
@@ -16934,24 +16979,24 @@
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="0" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B484" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D484" s="0" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E484" s="0" t="s">
         <v>2013</v>
       </c>
-      <c r="E484" s="0" t="s">
-        <v>2012</v>
-      </c>
       <c r="F484" s="0" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="0" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B485" s="0" t="s">
         <v>531</v>
@@ -16966,86 +17011,86 @@
         <v>14</v>
       </c>
       <c r="J485" s="0" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="K485" s="0" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="L485" s="0" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="0" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B486" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D486" s="0" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E486" s="0" t="s">
         <v>2020</v>
       </c>
-      <c r="E486" s="0" t="s">
-        <v>2019</v>
-      </c>
       <c r="F486" s="0" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="0" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B487" s="0" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E487" s="0" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F487" s="0" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="0" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B488" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D488" s="0" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E488" s="0" t="s">
         <v>2027</v>
       </c>
-      <c r="E488" s="0" t="s">
-        <v>2026</v>
-      </c>
       <c r="F488" s="0" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="0" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B489" s="0" t="s">
         <v>682</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="F489" s="0" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="0" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B490" s="0" t="s">
         <v>189</v>
@@ -17060,138 +17105,138 @@
         <v>14</v>
       </c>
       <c r="J490" s="0" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="K490" s="0" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="L490" s="0" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="0" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B491" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D491" s="0" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="E491" s="0" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="F491" s="0" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="J491" s="0" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="K491" s="0" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="L491" s="0" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="0" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B492" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D492" s="0" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="F492" s="0" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="J492" s="0" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="K492" s="0" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="L492" s="0" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="0" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B493" s="0" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="D493" s="0" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="F493" s="0" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="0" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B494" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D494" s="0" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E494" s="0" t="s">
         <v>2057</v>
       </c>
-      <c r="E494" s="0" t="s">
-        <v>2056</v>
-      </c>
       <c r="F494" s="0" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="0" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B495" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D495" s="0" t="s">
+        <v>2061</v>
+      </c>
+      <c r="E495" s="0" t="s">
         <v>2060</v>
       </c>
-      <c r="E495" s="0" t="s">
-        <v>2059</v>
-      </c>
       <c r="F495" s="0" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="0" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="B496" s="0" t="s">
         <v>561</v>
       </c>
       <c r="D496" s="0" t="s">
+        <v>2064</v>
+      </c>
+      <c r="E496" s="0" t="s">
         <v>2063</v>
       </c>
-      <c r="E496" s="0" t="s">
-        <v>2062</v>
-      </c>
       <c r="F496" s="0" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="0" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="B497" s="0" t="s">
         <v>13</v>
@@ -17206,18 +17251,18 @@
         <v>14</v>
       </c>
       <c r="J497" s="0" t="s">
+        <v>2067</v>
+      </c>
+      <c r="K497" s="0" t="s">
         <v>2066</v>
       </c>
-      <c r="K497" s="0" t="s">
-        <v>2065</v>
-      </c>
       <c r="L497" s="0" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="0" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="B498" s="0" t="s">
         <v>13</v>
@@ -17232,18 +17277,18 @@
         <v>14</v>
       </c>
       <c r="J498" s="0" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="K498" s="0" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="0" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="B499" s="0" t="s">
         <v>13</v>
@@ -17258,18 +17303,18 @@
         <v>14</v>
       </c>
       <c r="J499" s="0" t="s">
+        <v>2067</v>
+      </c>
+      <c r="K499" s="0" t="s">
         <v>2066</v>
       </c>
-      <c r="K499" s="0" t="s">
-        <v>2065</v>
-      </c>
       <c r="L499" s="0" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="0" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B500" s="0" t="s">
         <v>916</v>
@@ -17284,711 +17329,763 @@
         <v>14</v>
       </c>
       <c r="J500" s="0" t="s">
+        <v>2067</v>
+      </c>
+      <c r="K500" s="0" t="s">
         <v>2066</v>
       </c>
-      <c r="K500" s="0" t="s">
-        <v>2065</v>
-      </c>
       <c r="L500" s="0" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="0" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="B501" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D501" s="0" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="E501" s="0" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="F501" s="0" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="J501" s="0" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="K501" s="0" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="L501" s="0" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="0" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="B502" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D502" s="0" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="E502" s="0" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="F502" s="0" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="J502" s="0" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="K502" s="0" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="L502" s="0" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="0" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B503" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D503" s="0" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E503" s="0" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F503" s="0" t="s">
+        <v>2092</v>
+      </c>
+      <c r="J503" s="0" t="s">
+        <v>2086</v>
+      </c>
+      <c r="K503" s="0" t="s">
+        <v>2087</v>
+      </c>
+      <c r="L503" s="0" t="s">
         <v>2088</v>
-      </c>
-      <c r="B503" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D503" s="0" t="s">
-        <v>2089</v>
-      </c>
-      <c r="E503" s="0" t="s">
-        <v>2090</v>
-      </c>
-      <c r="F503" s="0" t="s">
-        <v>2091</v>
-      </c>
-      <c r="J503" s="0" t="s">
-        <v>2085</v>
-      </c>
-      <c r="K503" s="0" t="s">
-        <v>2086</v>
-      </c>
-      <c r="L503" s="0" t="s">
-        <v>2087</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="0" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="B504" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D504" s="0" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="E504" s="0" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="F504" s="0" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="J504" s="0" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="K504" s="0" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="L504" s="0" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="0" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B505" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D505" s="0" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="E505" s="0" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="F505" s="0" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="J505" s="0" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="K505" s="0" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="L505" s="0" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="0" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="B506" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D506" s="0" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="E506" s="0" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="F506" s="0" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="0" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="B507" s="0" t="s">
         <v>29</v>
       </c>
       <c r="D507" s="0" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="E507" s="0" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="F507" s="0" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="0" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="B508" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D508" s="0" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="E508" s="0" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="F508" s="0" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="J508" s="0" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="K508" s="0" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="L508" s="0" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="0" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B509" s="0" t="s">
         <v>263</v>
       </c>
       <c r="D509" s="0" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E509" s="0" t="s">
         <v>2119</v>
       </c>
-      <c r="E509" s="0" t="s">
-        <v>2118</v>
-      </c>
       <c r="F509" s="0" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="0" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="B510" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D510" s="0" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="E510" s="0" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="F510" s="0" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="0" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="B511" s="0" t="s">
         <v>29</v>
       </c>
       <c r="D511" s="0" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="E511" s="0" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="F511" s="0" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="0" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B512" s="0" t="s">
         <v>158</v>
       </c>
       <c r="D512" s="0" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="E512" s="0" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="F512" s="0" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="0" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="B513" s="0" t="s">
         <v>335</v>
       </c>
       <c r="D513" s="0" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="E513" s="0" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="F513" s="0" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="0" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="B514" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D514" s="0" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="E514" s="0" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="F514" s="0" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="0" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="B515" s="0" t="s">
         <v>291</v>
       </c>
       <c r="D515" s="0" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="E515" s="0" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="F515" s="0" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="0" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B516" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D516" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E516" s="0" t="s">
         <v>2146</v>
       </c>
-      <c r="E516" s="0" t="s">
-        <v>2145</v>
-      </c>
       <c r="F516" s="0" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="0" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B517" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D517" s="0" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="E517" s="0" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="F517" s="0" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="0" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="B518" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D518" s="0" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="E518" s="0" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="F518" s="0" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="J518" s="0" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="K518" s="0" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="L518" s="0" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="0" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="B519" s="0" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D519" s="0" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="E519" s="0" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="F519" s="0" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="0" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="B520" s="0" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D520" s="0" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="E520" s="0" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="F520" s="0" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="J520" s="0" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="K520" s="0" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="L520" s="0" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="0" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="B521" s="0" t="s">
         <v>449</v>
       </c>
       <c r="D521" s="0" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="E521" s="0" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="F521" s="0" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="J521" s="0" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="K521" s="0" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="L521" s="0" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="0" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="B522" s="0" t="s">
         <v>531</v>
       </c>
       <c r="D522" s="0" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="E522" s="0" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="F522" s="0" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="J522" s="0" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="K522" s="0" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="L522" s="0" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="0" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="B523" s="0" t="s">
         <v>219</v>
       </c>
       <c r="D523" s="0" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="E523" s="0" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="F523" s="0" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="J523" s="0" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="K523" s="0" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="L523" s="0" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="0" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="B524" s="0" t="s">
-        <v>13</v>
+        <v>948</v>
       </c>
       <c r="D524" s="0" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="E524" s="0" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="F524" s="0" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="J524" s="0" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="K524" s="0" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="L524" s="0" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="0" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="B525" s="0" t="s">
-        <v>13</v>
+        <v>948</v>
       </c>
       <c r="D525" s="0" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="E525" s="0" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="F525" s="0" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="J525" s="0" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="K525" s="0" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="L525" s="0" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="0" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B526" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D526" s="0" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="E526" s="0" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="F526" s="0" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="J526" s="0" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="K526" s="0" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="L526" s="0" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="0" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="B527" s="0" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D527" s="0" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="E527" s="0" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="F527" s="0" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="J527" s="0" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="K527" s="0" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="L527" s="0" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="0" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="B528" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D528" s="0" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="E528" s="0" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="F528" s="0" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="J528" s="0" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="K528" s="0" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="L528" s="0" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="0" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="B529" s="0" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D529" s="0" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="E529" s="0" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="F529" s="0" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="J529" s="0" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="K529" s="0" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="L529" s="0" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="0" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="B530" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D530" s="0" t="s">
-        <v>1371</v>
+        <v>2232</v>
       </c>
       <c r="E530" s="0" t="s">
-        <v>1372</v>
+        <v>2233</v>
       </c>
       <c r="F530" s="0" t="s">
-        <v>1373</v>
+        <v>2234</v>
       </c>
       <c r="J530" s="0" t="s">
-        <v>2231</v>
+        <v>2235</v>
       </c>
       <c r="K530" s="0" t="s">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="L530" s="0" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="0" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="B531" s="0" t="s">
-        <v>2235</v>
+        <v>13</v>
       </c>
       <c r="D531" s="0" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
       <c r="E531" s="0" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F531" s="0" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="J531" s="0" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="K531" s="0" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="L531" s="0" t="s">
-        <v>2241</v>
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A532" s="0" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B532" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D532" s="0" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E532" s="0" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F532" s="0" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J532" s="0" t="s">
+        <v>2246</v>
+      </c>
+      <c r="K532" s="0" t="s">
+        <v>2247</v>
+      </c>
+      <c r="L532" s="0" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="0" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B533" s="0" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D533" s="0" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E533" s="0" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F533" s="0" t="s">
+        <v>2253</v>
+      </c>
+      <c r="J533" s="0" t="s">
+        <v>2254</v>
+      </c>
+      <c r="K533" s="0" t="s">
+        <v>2255</v>
+      </c>
+      <c r="L533" s="0" t="s">
+        <v>2256</v>
       </c>
     </row>
   </sheetData>
